--- a/artfynd/A 43249-2024 artfynd.xlsx
+++ b/artfynd/A 43249-2024 artfynd.xlsx
@@ -1341,7 +1341,7 @@
         <v>120656976</v>
       </c>
       <c r="B8" t="n">
-        <v>56240</v>
+        <v>56243</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
